--- a/data/nzd0337/nzd0337.xlsx
+++ b/data/nzd0337/nzd0337.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I451"/>
+  <dimension ref="A1:I452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15257,6 +15257,39 @@
         <v>184.88</v>
       </c>
       <c r="I451" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>397.45</v>
+      </c>
+      <c r="C452" t="n">
+        <v>385.01</v>
+      </c>
+      <c r="D452" t="n">
+        <v>374.11</v>
+      </c>
+      <c r="E452" t="n">
+        <v>365.95</v>
+      </c>
+      <c r="F452" t="n">
+        <v>365.18</v>
+      </c>
+      <c r="G452" t="n">
+        <v>362.57</v>
+      </c>
+      <c r="H452" t="n">
+        <v>215.56</v>
+      </c>
+      <c r="I452" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15273,7 +15306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B536"/>
+  <dimension ref="A1:B537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20636,6 +20669,16 @@
       </c>
       <c r="B536" t="n">
         <v>-0.98</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>
@@ -20804,28 +20847,28 @@
         <v>0.0805</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7465843353523731</v>
+        <v>0.7472741283677929</v>
       </c>
       <c r="J2" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K2" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L2" t="n">
-        <v>0.349614517632586</v>
+        <v>0.3508904691551078</v>
       </c>
       <c r="M2" t="n">
-        <v>6.277004349278816</v>
+        <v>6.26768364143664</v>
       </c>
       <c r="N2" t="n">
-        <v>66.13911581728669</v>
+        <v>66.00028935190279</v>
       </c>
       <c r="O2" t="n">
-        <v>8.132595884297135</v>
+        <v>8.124056212995008</v>
       </c>
       <c r="P2" t="n">
-        <v>375.8743727820146</v>
+        <v>375.8676367694203</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20882,28 +20925,28 @@
         <v>0.1602</v>
       </c>
       <c r="I3" t="n">
-        <v>1.207474861984255</v>
+        <v>1.208842774602731</v>
       </c>
       <c r="J3" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K3" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5882370825142511</v>
+        <v>0.5896126267892949</v>
       </c>
       <c r="M3" t="n">
-        <v>6.235004215890962</v>
+        <v>6.229466410917818</v>
       </c>
       <c r="N3" t="n">
-        <v>64.31816515763919</v>
+        <v>64.20490645994781</v>
       </c>
       <c r="O3" t="n">
-        <v>8.019860669465473</v>
+        <v>8.012796419474776</v>
       </c>
       <c r="P3" t="n">
-        <v>349.4760804275541</v>
+        <v>349.462574351131</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20960,28 +21003,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.316351712437861</v>
+        <v>1.316762621406047</v>
       </c>
       <c r="J4" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K4" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6509318210033415</v>
+        <v>0.6519446396813368</v>
       </c>
       <c r="M4" t="n">
-        <v>5.829805868652772</v>
+        <v>5.819818010875404</v>
       </c>
       <c r="N4" t="n">
-        <v>58.07914141215312</v>
+        <v>57.95104944820215</v>
       </c>
       <c r="O4" t="n">
-        <v>7.620967222876183</v>
+        <v>7.612558666322523</v>
       </c>
       <c r="P4" t="n">
-        <v>338.2911835001427</v>
+        <v>338.2870888374043</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21038,28 +21081,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1.30293012825105</v>
+        <v>1.301179361618336</v>
       </c>
       <c r="J5" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K5" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6096932807351587</v>
+        <v>0.60980513327174</v>
       </c>
       <c r="M5" t="n">
-        <v>5.750083925653281</v>
+        <v>5.746951417527373</v>
       </c>
       <c r="N5" t="n">
-        <v>68.21617997325772</v>
+        <v>68.11272264162938</v>
       </c>
       <c r="O5" t="n">
-        <v>8.259308686158771</v>
+        <v>8.253043235172671</v>
       </c>
       <c r="P5" t="n">
-        <v>336.3032016521036</v>
+        <v>336.3205662343439</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21116,28 +21159,28 @@
         <v>0.1923</v>
       </c>
       <c r="I6" t="n">
-        <v>1.183237397771989</v>
+        <v>1.181780289774554</v>
       </c>
       <c r="J6" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K6" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L6" t="n">
-        <v>0.61958957627508</v>
+        <v>0.6197759954342298</v>
       </c>
       <c r="M6" t="n">
-        <v>5.492046755951454</v>
+        <v>5.48930405007939</v>
       </c>
       <c r="N6" t="n">
-        <v>53.89885749228147</v>
+        <v>53.81248083752747</v>
       </c>
       <c r="O6" t="n">
-        <v>7.341584126895331</v>
+        <v>7.335699069449856</v>
       </c>
       <c r="P6" t="n">
-        <v>337.8952899393474</v>
+        <v>337.909743283237</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21194,28 +21237,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.147991867666736</v>
+        <v>1.145788965690007</v>
       </c>
       <c r="J7" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K7" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L7" t="n">
-        <v>0.455898939694516</v>
+        <v>0.4557100087600792</v>
       </c>
       <c r="M7" t="n">
-        <v>7.272317841930706</v>
+        <v>7.269915526804399</v>
       </c>
       <c r="N7" t="n">
-        <v>99.27700111621309</v>
+        <v>99.13288916754445</v>
       </c>
       <c r="O7" t="n">
-        <v>9.963784477607547</v>
+        <v>9.956550063528253</v>
       </c>
       <c r="P7" t="n">
-        <v>338.2419144433852</v>
+        <v>338.2636853760759</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21272,28 +21315,28 @@
         <v>0.1378</v>
       </c>
       <c r="I8" t="n">
-        <v>3.789750586653437</v>
+        <v>3.747706482539004</v>
       </c>
       <c r="J8" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K8" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1147756593137205</v>
+        <v>0.1124969775945104</v>
       </c>
       <c r="M8" t="n">
-        <v>74.62829010662257</v>
+        <v>74.77444087244361</v>
       </c>
       <c r="N8" t="n">
-        <v>7099.299858584155</v>
+        <v>7112.754430938561</v>
       </c>
       <c r="O8" t="n">
-        <v>84.25734305438402</v>
+        <v>84.33714739626045</v>
       </c>
       <c r="P8" t="n">
-        <v>230.2511790723284</v>
+        <v>230.6626378617499</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21331,7 +21374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I451"/>
+  <dimension ref="A1:I452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42399,6 +42442,53 @@
         </is>
       </c>
     </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>-41.06706116592438,172.10436117882423</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>-41.06637545506621,172.10436251198513</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>-41.0656918796367,172.10434573388568</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-41.0650121088977,172.10429673490395</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>-41.064342611142386,172.10416083960797</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>-41.063670547130144,172.10404657931906</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>-41.06279760124907,172.10563018824908</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0337/nzd0337.xlsx
+++ b/data/nzd0337/nzd0337.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I452"/>
+  <dimension ref="A1:I455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15290,6 +15290,105 @@
         <v>215.56</v>
       </c>
       <c r="I452" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>398.58</v>
+      </c>
+      <c r="C453" t="n">
+        <v>385.66</v>
+      </c>
+      <c r="D453" t="n">
+        <v>374.31</v>
+      </c>
+      <c r="E453" t="n">
+        <v>367.05</v>
+      </c>
+      <c r="F453" t="n">
+        <v>367.19</v>
+      </c>
+      <c r="G453" t="n">
+        <v>365.62</v>
+      </c>
+      <c r="H453" t="n">
+        <v>280.11</v>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>396.9</v>
+      </c>
+      <c r="C454" t="n">
+        <v>385.01</v>
+      </c>
+      <c r="D454" t="n">
+        <v>374.2</v>
+      </c>
+      <c r="E454" t="n">
+        <v>367.72</v>
+      </c>
+      <c r="F454" t="n">
+        <v>367.8</v>
+      </c>
+      <c r="G454" t="n">
+        <v>366.52</v>
+      </c>
+      <c r="H454" t="n">
+        <v>320.26</v>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:19:21+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>396.75</v>
+      </c>
+      <c r="C455" t="n">
+        <v>385.04</v>
+      </c>
+      <c r="D455" t="n">
+        <v>373.95</v>
+      </c>
+      <c r="E455" t="n">
+        <v>367.83</v>
+      </c>
+      <c r="F455" t="n">
+        <v>368.59</v>
+      </c>
+      <c r="G455" t="n">
+        <v>367.55</v>
+      </c>
+      <c r="H455" t="n">
+        <v>326.46</v>
+      </c>
+      <c r="I455" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15306,7 +15405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B537"/>
+  <dimension ref="A1:B540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20679,6 +20778,36 @@
       </c>
       <c r="B537" t="n">
         <v>-0.1</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>
@@ -20847,28 +20976,28 @@
         <v>0.0805</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7472741283677929</v>
+        <v>0.7491853441826621</v>
       </c>
       <c r="J2" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K2" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3508904691551078</v>
+        <v>0.3546382592453573</v>
       </c>
       <c r="M2" t="n">
-        <v>6.26768364143664</v>
+        <v>6.238908801711513</v>
       </c>
       <c r="N2" t="n">
-        <v>66.00028935190279</v>
+        <v>65.58879868954988</v>
       </c>
       <c r="O2" t="n">
-        <v>8.124056212995008</v>
+        <v>8.098691171389971</v>
       </c>
       <c r="P2" t="n">
-        <v>375.8676367694203</v>
+        <v>375.8488627622665</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20925,28 +21054,28 @@
         <v>0.1602</v>
       </c>
       <c r="I3" t="n">
-        <v>1.208842774602731</v>
+        <v>1.212983950489158</v>
       </c>
       <c r="J3" t="n">
+        <v>454</v>
+      </c>
+      <c r="K3" t="n">
         <v>451</v>
       </c>
-      <c r="K3" t="n">
-        <v>448</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.5896126267892949</v>
+        <v>0.5937437054919062</v>
       </c>
       <c r="M3" t="n">
-        <v>6.229466410917818</v>
+        <v>6.213207787047626</v>
       </c>
       <c r="N3" t="n">
-        <v>64.20490645994781</v>
+        <v>63.87083455926892</v>
       </c>
       <c r="O3" t="n">
-        <v>8.012796419474776</v>
+        <v>7.991923082667207</v>
       </c>
       <c r="P3" t="n">
-        <v>349.462574351131</v>
+        <v>349.4214309391967</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21003,28 +21132,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.316762621406047</v>
+        <v>1.317866197684033</v>
       </c>
       <c r="J4" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K4" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6519446396813368</v>
+        <v>0.6549468561180973</v>
       </c>
       <c r="M4" t="n">
-        <v>5.819818010875404</v>
+        <v>5.789070982639741</v>
       </c>
       <c r="N4" t="n">
-        <v>57.95104944820215</v>
+        <v>57.56883560901377</v>
       </c>
       <c r="O4" t="n">
-        <v>7.612558666322523</v>
+        <v>7.587412972088297</v>
       </c>
       <c r="P4" t="n">
-        <v>338.2870888374043</v>
+        <v>338.27602413509</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21081,28 +21210,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1.301179361618336</v>
+        <v>1.297596912408118</v>
       </c>
       <c r="J5" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K5" t="n">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="L5" t="n">
-        <v>0.60980513327174</v>
+        <v>0.6110334955581727</v>
       </c>
       <c r="M5" t="n">
-        <v>5.746951417527373</v>
+        <v>5.728532645730844</v>
       </c>
       <c r="N5" t="n">
-        <v>68.11272264162938</v>
+        <v>67.72720630543614</v>
       </c>
       <c r="O5" t="n">
-        <v>8.253043235172671</v>
+        <v>8.229654081760431</v>
       </c>
       <c r="P5" t="n">
-        <v>336.3205662343439</v>
+        <v>336.3563195109861</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21159,28 +21288,28 @@
         <v>0.1923</v>
       </c>
       <c r="I6" t="n">
-        <v>1.181780289774554</v>
+        <v>1.18029322528014</v>
       </c>
       <c r="J6" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K6" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6197759954342298</v>
+        <v>0.6218814534506849</v>
       </c>
       <c r="M6" t="n">
-        <v>5.48930405007939</v>
+        <v>5.462328784030928</v>
       </c>
       <c r="N6" t="n">
-        <v>53.81248083752747</v>
+        <v>53.46762152584149</v>
       </c>
       <c r="O6" t="n">
-        <v>7.335699069449856</v>
+        <v>7.312155737252968</v>
       </c>
       <c r="P6" t="n">
-        <v>337.909743283237</v>
+        <v>337.9245805421611</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21237,28 +21366,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.145788965690007</v>
+        <v>1.143539538315368</v>
       </c>
       <c r="J7" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K7" t="n">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4557100087600792</v>
+        <v>0.457553617684295</v>
       </c>
       <c r="M7" t="n">
-        <v>7.269915526804399</v>
+        <v>7.235233683639622</v>
       </c>
       <c r="N7" t="n">
-        <v>99.13288916754445</v>
+        <v>98.50042252095612</v>
       </c>
       <c r="O7" t="n">
-        <v>9.956550063528253</v>
+        <v>9.924737906915029</v>
       </c>
       <c r="P7" t="n">
-        <v>338.2636853760759</v>
+        <v>338.2860492031508</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21315,28 +21444,28 @@
         <v>0.1378</v>
       </c>
       <c r="I8" t="n">
-        <v>3.747706482539004</v>
+        <v>3.724857683411575</v>
       </c>
       <c r="J8" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K8" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1124969775945104</v>
+        <v>0.1123505544160054</v>
       </c>
       <c r="M8" t="n">
-        <v>74.77444087244361</v>
+        <v>74.43992067228926</v>
       </c>
       <c r="N8" t="n">
-        <v>7112.754430938561</v>
+        <v>7070.634938946339</v>
       </c>
       <c r="O8" t="n">
-        <v>84.33714739626045</v>
+        <v>84.08706760820203</v>
       </c>
       <c r="P8" t="n">
-        <v>230.6626378617499</v>
+        <v>230.887488910615</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21374,7 +21503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I452"/>
+  <dimension ref="A1:I455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42489,6 +42618,147 @@
         </is>
       </c>
     </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>-41.06706273777857,172.10434789131384</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>-41.06637635923439,172.10435486880726</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>-41.06569215784323,172.1043433821632</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-41.06501363903421,172.10428380056356</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>-41.064345407102316,172.10413720527706</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>-41.06367478973693,172.10401071664103</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>-41.062887399981946,172.10487120402965</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>-41.06706040086202,172.10436764619635</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>-41.06637545506621,172.10436251198513</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>-41.06569200482964,172.10434467561055</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-41.06501457102575,172.10427592237414</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>-41.06434625562651,172.10413003266876</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>-41.06367604165155,172.1040001342106</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>-41.06294325212135,172.10439911602342</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:19:21+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>-41.067060192208594,172.10436941002507</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>-41.06637549679706,172.1043621592231</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>-41.06569165707145,172.10434761526363</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-41.06501472403923,172.10427462894003</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>-41.06434735453421,172.1041207435529</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>-41.063677474397075,172.10398802320643</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>-41.062951876687016,172.10432621569024</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0337/nzd0337.xlsx
+++ b/data/nzd0337/nzd0337.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I455"/>
+  <dimension ref="A1:I457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15389,6 +15389,72 @@
         <v>326.46</v>
       </c>
       <c r="I455" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>394.63</v>
+      </c>
+      <c r="C456" t="n">
+        <v>383.88</v>
+      </c>
+      <c r="D456" t="n">
+        <v>373.65</v>
+      </c>
+      <c r="E456" t="n">
+        <v>368.29</v>
+      </c>
+      <c r="F456" t="n">
+        <v>370.18</v>
+      </c>
+      <c r="G456" t="n">
+        <v>368.75</v>
+      </c>
+      <c r="H456" t="n">
+        <v>370.13</v>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:25+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>393.98</v>
+      </c>
+      <c r="C457" t="n">
+        <v>383.6</v>
+      </c>
+      <c r="D457" t="n">
+        <v>373.57</v>
+      </c>
+      <c r="E457" t="n">
+        <v>368.62</v>
+      </c>
+      <c r="F457" t="n">
+        <v>370.1</v>
+      </c>
+      <c r="G457" t="n">
+        <v>368.85</v>
+      </c>
+      <c r="H457" t="n">
+        <v>371.05</v>
+      </c>
+      <c r="I457" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15405,7 +15471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B540"/>
+  <dimension ref="A1:B542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20808,6 +20874,26 @@
       </c>
       <c r="B540" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>-0.04</v>
       </c>
     </row>
   </sheetData>
@@ -20976,28 +21062,28 @@
         <v>0.0805</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7491853441826621</v>
+        <v>0.7481485161931162</v>
       </c>
       <c r="J2" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K2" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3546382592453573</v>
+        <v>0.35574005845558</v>
       </c>
       <c r="M2" t="n">
-        <v>6.238908801711513</v>
+        <v>6.217196555745534</v>
       </c>
       <c r="N2" t="n">
-        <v>65.58879868954988</v>
+        <v>65.31056335016204</v>
       </c>
       <c r="O2" t="n">
-        <v>8.098691171389971</v>
+        <v>8.08149511848903</v>
       </c>
       <c r="P2" t="n">
-        <v>375.8488627622665</v>
+        <v>375.8590950556276</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21054,28 +21140,28 @@
         <v>0.1602</v>
       </c>
       <c r="I3" t="n">
-        <v>1.212983950489158</v>
+        <v>1.214529157554681</v>
       </c>
       <c r="J3" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K3" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5937437054919062</v>
+        <v>0.596149928249373</v>
       </c>
       <c r="M3" t="n">
-        <v>6.213207787047626</v>
+        <v>6.195141090312055</v>
       </c>
       <c r="N3" t="n">
-        <v>63.87083455926892</v>
+        <v>63.60852338967667</v>
       </c>
       <c r="O3" t="n">
-        <v>7.991923082667207</v>
+        <v>7.975495181471597</v>
       </c>
       <c r="P3" t="n">
-        <v>349.4214309391967</v>
+        <v>349.4060203212426</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21132,28 +21218,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.317866197684033</v>
+        <v>1.318120815979055</v>
       </c>
       <c r="J4" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K4" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6549468561180973</v>
+        <v>0.6567780948438284</v>
       </c>
       <c r="M4" t="n">
-        <v>5.789070982639741</v>
+        <v>5.765183737706537</v>
       </c>
       <c r="N4" t="n">
-        <v>57.56883560901377</v>
+        <v>57.31295336389083</v>
       </c>
       <c r="O4" t="n">
-        <v>7.587412972088297</v>
+        <v>7.57053190759347</v>
       </c>
       <c r="P4" t="n">
-        <v>338.27602413509</v>
+        <v>338.2734616558499</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21210,28 +21296,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1.297596912408118</v>
+        <v>1.295874813961462</v>
       </c>
       <c r="J5" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K5" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6110334955581727</v>
+        <v>0.6121561465367011</v>
       </c>
       <c r="M5" t="n">
-        <v>5.728532645730844</v>
+        <v>5.712650947952155</v>
       </c>
       <c r="N5" t="n">
-        <v>67.72720630543614</v>
+        <v>67.45114139898905</v>
       </c>
       <c r="O5" t="n">
-        <v>8.229654081760431</v>
+        <v>8.212864384548734</v>
       </c>
       <c r="P5" t="n">
-        <v>336.3563195109861</v>
+        <v>336.3735728874809</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21288,28 +21374,28 @@
         <v>0.1923</v>
       </c>
       <c r="I6" t="n">
-        <v>1.18029322528014</v>
+        <v>1.180936210057137</v>
       </c>
       <c r="J6" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K6" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6218814534506849</v>
+        <v>0.6239432306210148</v>
       </c>
       <c r="M6" t="n">
-        <v>5.462328784030928</v>
+        <v>5.441718740731152</v>
       </c>
       <c r="N6" t="n">
-        <v>53.46762152584149</v>
+        <v>53.23442499077431</v>
       </c>
       <c r="O6" t="n">
-        <v>7.312155737252968</v>
+        <v>7.296192499569506</v>
       </c>
       <c r="P6" t="n">
-        <v>337.9245805421611</v>
+        <v>337.9181383982715</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21366,28 +21452,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.143539538315368</v>
+        <v>1.143653768752713</v>
       </c>
       <c r="J7" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K7" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L7" t="n">
-        <v>0.457553617684295</v>
+        <v>0.4595205104183049</v>
       </c>
       <c r="M7" t="n">
-        <v>7.235233683639622</v>
+        <v>7.203746748840001</v>
       </c>
       <c r="N7" t="n">
-        <v>98.50042252095612</v>
+        <v>98.0627519624894</v>
       </c>
       <c r="O7" t="n">
-        <v>9.924737906915029</v>
+        <v>9.902663882132392</v>
       </c>
       <c r="P7" t="n">
-        <v>338.2860492031508</v>
+        <v>338.2849084525329</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21444,28 +21530,28 @@
         <v>0.1378</v>
       </c>
       <c r="I8" t="n">
-        <v>3.724857683411575</v>
+        <v>3.754394915692805</v>
       </c>
       <c r="J8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K8" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1123505544160054</v>
+        <v>0.1146046635087884</v>
       </c>
       <c r="M8" t="n">
-        <v>74.43992067228926</v>
+        <v>74.25244293243743</v>
       </c>
       <c r="N8" t="n">
-        <v>7070.634938946339</v>
+        <v>7046.417868983893</v>
       </c>
       <c r="O8" t="n">
-        <v>84.08706760820203</v>
+        <v>83.9429441286395</v>
       </c>
       <c r="P8" t="n">
-        <v>230.887488910615</v>
+        <v>230.595375742147</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21503,7 +21589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I455"/>
+  <dimension ref="A1:I457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42759,6 +42845,100 @@
         </is>
       </c>
     </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>-41.06705724323723,172.10439433880333</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>-41.06637388320338,172.10437579935547</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>-41.0656912397615,172.10435114284732</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>-41.06501536391363,172.10426922003373</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>-41.06434956625757,172.10410204773646</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>-41.063679143613555,172.103973913298</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>-41.063012622920084,172.10381273814937</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:25+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>-41.06705633907038,172.10440198206038</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>-41.06637349371501,172.10437909180112</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>-41.06569112847883,172.1043520835363</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>-41.065015822953804,172.1042653397313</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>-41.06434945497596,172.10410298840648</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>-41.06367928271486,172.10397273747228</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>-41.06301390264198,172.10380192065998</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0337/nzd0337.xlsx
+++ b/data/nzd0337/nzd0337.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I457"/>
+  <dimension ref="A1:I460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15455,6 +15455,105 @@
         <v>371.05</v>
       </c>
       <c r="I457" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>394</v>
+      </c>
+      <c r="C458" t="n">
+        <v>383.41</v>
+      </c>
+      <c r="D458" t="n">
+        <v>373.52</v>
+      </c>
+      <c r="E458" t="n">
+        <v>369.19</v>
+      </c>
+      <c r="F458" t="n">
+        <v>370.94</v>
+      </c>
+      <c r="G458" t="n">
+        <v>369.97</v>
+      </c>
+      <c r="H458" t="n">
+        <v>373.13</v>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>396.66</v>
+      </c>
+      <c r="C459" t="n">
+        <v>386.85</v>
+      </c>
+      <c r="D459" t="n">
+        <v>375.03</v>
+      </c>
+      <c r="E459" t="n">
+        <v>371.44</v>
+      </c>
+      <c r="F459" t="n">
+        <v>374.51</v>
+      </c>
+      <c r="G459" t="n">
+        <v>374.62</v>
+      </c>
+      <c r="H459" t="n">
+        <v>355.49</v>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>397.44</v>
+      </c>
+      <c r="C460" t="n">
+        <v>387.82</v>
+      </c>
+      <c r="D460" t="n">
+        <v>376.25</v>
+      </c>
+      <c r="E460" t="n">
+        <v>372.22</v>
+      </c>
+      <c r="F460" t="n">
+        <v>374.18</v>
+      </c>
+      <c r="G460" t="n">
+        <v>374.62</v>
+      </c>
+      <c r="H460" t="n">
+        <v>333.27</v>
+      </c>
+      <c r="I460" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15471,7 +15570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B542"/>
+  <dimension ref="A1:B545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20894,6 +20993,36 @@
       </c>
       <c r="B542" t="n">
         <v>-0.04</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
@@ -21062,28 +21191,28 @@
         <v>0.0805</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7481485161931162</v>
+        <v>0.7484148167056035</v>
       </c>
       <c r="J2" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K2" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L2" t="n">
-        <v>0.35574005845558</v>
+        <v>0.3585071106498388</v>
       </c>
       <c r="M2" t="n">
-        <v>6.217196555745534</v>
+        <v>6.185924541022245</v>
       </c>
       <c r="N2" t="n">
-        <v>65.31056335016204</v>
+        <v>64.89769617148788</v>
       </c>
       <c r="O2" t="n">
-        <v>8.08149511848903</v>
+        <v>8.055910635768489</v>
       </c>
       <c r="P2" t="n">
-        <v>375.8590950556276</v>
+        <v>375.8564211670824</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21140,28 +21269,28 @@
         <v>0.1602</v>
       </c>
       <c r="I3" t="n">
-        <v>1.214529157554681</v>
+        <v>1.21916322795723</v>
       </c>
       <c r="J3" t="n">
+        <v>459</v>
+      </c>
+      <c r="K3" t="n">
         <v>456</v>
       </c>
-      <c r="K3" t="n">
-        <v>453</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.596149928249373</v>
+        <v>0.6002348940538866</v>
       </c>
       <c r="M3" t="n">
-        <v>6.195141090312055</v>
+        <v>6.181991410179037</v>
       </c>
       <c r="N3" t="n">
-        <v>63.60852338967667</v>
+        <v>63.33002014296383</v>
       </c>
       <c r="O3" t="n">
-        <v>7.975495181471597</v>
+        <v>7.958016093409451</v>
       </c>
       <c r="P3" t="n">
-        <v>349.4060203212426</v>
+        <v>349.3595053256727</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21218,28 +21347,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.318120815979055</v>
+        <v>1.319810151895175</v>
       </c>
       <c r="J4" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K4" t="n">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6567780948438284</v>
+        <v>0.6598669016042293</v>
       </c>
       <c r="M4" t="n">
-        <v>5.765183737706537</v>
+        <v>5.739311914213371</v>
       </c>
       <c r="N4" t="n">
-        <v>57.31295336389083</v>
+        <v>56.95559680783443</v>
       </c>
       <c r="O4" t="n">
-        <v>7.57053190759347</v>
+        <v>7.546893189109968</v>
       </c>
       <c r="P4" t="n">
-        <v>338.2734616558499</v>
+        <v>338.2563390454026</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21296,28 +21425,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1.295874813961462</v>
+        <v>1.295934956874065</v>
       </c>
       <c r="J5" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K5" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6121561465367011</v>
+        <v>0.6148888269963948</v>
       </c>
       <c r="M5" t="n">
-        <v>5.712650947952155</v>
+        <v>5.682496320753929</v>
       </c>
       <c r="N5" t="n">
-        <v>67.45114139898905</v>
+        <v>67.01553432831126</v>
       </c>
       <c r="O5" t="n">
-        <v>8.212864384548734</v>
+        <v>8.186301627005401</v>
       </c>
       <c r="P5" t="n">
-        <v>336.3735728874809</v>
+        <v>336.3729387614053</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21374,28 +21503,28 @@
         <v>0.1923</v>
       </c>
       <c r="I6" t="n">
-        <v>1.180936210057137</v>
+        <v>1.185111348960656</v>
       </c>
       <c r="J6" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K6" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6239432306210148</v>
+        <v>0.6278199111911578</v>
       </c>
       <c r="M6" t="n">
-        <v>5.441718740731152</v>
+        <v>5.428689940301484</v>
       </c>
       <c r="N6" t="n">
-        <v>53.23442499077431</v>
+        <v>52.99458158404502</v>
       </c>
       <c r="O6" t="n">
-        <v>7.296192499569506</v>
+        <v>7.279737741433068</v>
       </c>
       <c r="P6" t="n">
-        <v>337.9181383982715</v>
+        <v>337.8760416287541</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21452,28 +21581,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.143653768752713</v>
+        <v>1.148350339927102</v>
       </c>
       <c r="J7" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K7" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4595205104183049</v>
+        <v>0.4640422939713702</v>
       </c>
       <c r="M7" t="n">
-        <v>7.203746748840001</v>
+        <v>7.183108216791905</v>
       </c>
       <c r="N7" t="n">
-        <v>98.0627519624894</v>
+        <v>97.56518866264929</v>
       </c>
       <c r="O7" t="n">
-        <v>9.902663882132392</v>
+        <v>9.877509233741534</v>
       </c>
       <c r="P7" t="n">
-        <v>338.2849084525329</v>
+        <v>338.2377092984458</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21530,28 +21659,28 @@
         <v>0.1378</v>
       </c>
       <c r="I8" t="n">
-        <v>3.754394915692805</v>
+        <v>3.779444990957221</v>
       </c>
       <c r="J8" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K8" t="n">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1146046635087884</v>
+        <v>0.1170611013694215</v>
       </c>
       <c r="M8" t="n">
-        <v>74.25244293243743</v>
+        <v>73.87963154602365</v>
       </c>
       <c r="N8" t="n">
-        <v>7046.417868983893</v>
+        <v>7004.902422920471</v>
       </c>
       <c r="O8" t="n">
-        <v>83.9429441286395</v>
+        <v>83.69529510623921</v>
       </c>
       <c r="P8" t="n">
-        <v>230.595375742147</v>
+        <v>230.3466021795195</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21589,7 +21718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I457"/>
+  <dimension ref="A1:I460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42939,6 +43068,147 @@
         </is>
       </c>
     </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>-41.06705636689091,172.10440174688324</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>-41.06637322941928,172.10438132596065</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>-41.06569105892716,172.1043526714669</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-41.06501661584108,172.10425863739064</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>-41.064350623432446,172.10409311137096</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>-41.06368084064852,172.10395956822373</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>-41.06301679592247,172.1037774637259</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>-41.06706006701652,172.10437046832232</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>-41.066378014556356,172.1043408759118</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>-41.06569315938633,172.10433491596208</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-41.065019745655434,172.10423218078122</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-41.064355589362975,172.10405113396612</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>-41.063687308839135,172.10390489231946</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>-41.06299225851277,172.1039848772747</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>-41.06706115201414,172.10436129641283</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>-41.066379363851155,172.1043294699377</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>-41.06569485644407,172.10432057045406</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-41.06502083065631,172.10422300915607</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>-41.064355130328025,172.1040550142307</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>-41.063687308839135,172.10390489231946</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>-41.06296134974526,172.10424614288394</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0337/nzd0337.xlsx
+++ b/data/nzd0337/nzd0337.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I460"/>
+  <dimension ref="A1:I461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15518,7 +15518,7 @@
         <v>374.62</v>
       </c>
       <c r="H459" t="n">
-        <v>355.49</v>
+        <v>380.21</v>
       </c>
       <c r="I459" t="inlineStr">
         <is>
@@ -15551,9 +15551,42 @@
         <v>374.62</v>
       </c>
       <c r="H460" t="n">
-        <v>333.27</v>
+        <v>380.21</v>
       </c>
       <c r="I460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:06+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>396.21</v>
+      </c>
+      <c r="C461" t="n">
+        <v>386.5</v>
+      </c>
+      <c r="D461" t="n">
+        <v>373.92</v>
+      </c>
+      <c r="E461" t="n">
+        <v>370.15</v>
+      </c>
+      <c r="F461" t="n">
+        <v>372.98</v>
+      </c>
+      <c r="G461" t="n">
+        <v>373.03</v>
+      </c>
+      <c r="H461" t="n">
+        <v>380.9</v>
+      </c>
+      <c r="I461" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15570,7 +15603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B545"/>
+  <dimension ref="A1:B547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21023,6 +21056,26 @@
       </c>
       <c r="B545" t="n">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>1.75</v>
       </c>
     </row>
   </sheetData>
@@ -21191,28 +21244,28 @@
         <v>0.0805</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7484148167056035</v>
+        <v>0.7485468616047306</v>
       </c>
       <c r="J2" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K2" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3585071106498388</v>
+        <v>0.359468995335179</v>
       </c>
       <c r="M2" t="n">
-        <v>6.185924541022245</v>
+        <v>6.173349842211572</v>
       </c>
       <c r="N2" t="n">
-        <v>64.89769617148788</v>
+        <v>64.75690879181066</v>
       </c>
       <c r="O2" t="n">
-        <v>8.055910635768489</v>
+        <v>8.047167749699932</v>
       </c>
       <c r="P2" t="n">
-        <v>375.8564211670824</v>
+        <v>375.8551068506455</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21269,28 +21322,28 @@
         <v>0.1602</v>
       </c>
       <c r="I3" t="n">
-        <v>1.21916322795723</v>
+        <v>1.220822361386465</v>
       </c>
       <c r="J3" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K3" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6002348940538866</v>
+        <v>0.6016350851996568</v>
       </c>
       <c r="M3" t="n">
-        <v>6.181991410179037</v>
+        <v>6.178299924802202</v>
       </c>
       <c r="N3" t="n">
-        <v>63.33002014296383</v>
+        <v>63.23724918089884</v>
       </c>
       <c r="O3" t="n">
-        <v>7.958016093409451</v>
+        <v>7.952185182759443</v>
       </c>
       <c r="P3" t="n">
-        <v>349.3595053256727</v>
+        <v>349.3428103522193</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21347,28 +21400,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.319810151895175</v>
+        <v>1.319963283889876</v>
       </c>
       <c r="J4" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K4" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6598669016042293</v>
+        <v>0.6607782929658028</v>
       </c>
       <c r="M4" t="n">
-        <v>5.739311914213371</v>
+        <v>5.727760049235087</v>
       </c>
       <c r="N4" t="n">
-        <v>56.95559680783443</v>
+        <v>56.83025445729258</v>
       </c>
       <c r="O4" t="n">
-        <v>7.546893189109968</v>
+        <v>7.538584380193179</v>
       </c>
       <c r="P4" t="n">
-        <v>338.2563390454026</v>
+        <v>338.254783861405</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21425,28 +21478,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1.295934956874065</v>
+        <v>1.295635524688633</v>
       </c>
       <c r="J5" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K5" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6148888269963948</v>
+        <v>0.6156832696930499</v>
       </c>
       <c r="M5" t="n">
-        <v>5.682496320753929</v>
+        <v>5.671664461011424</v>
       </c>
       <c r="N5" t="n">
-        <v>67.01553432831126</v>
+        <v>66.86973438749045</v>
       </c>
       <c r="O5" t="n">
-        <v>8.186301627005401</v>
+        <v>8.177391661617442</v>
       </c>
       <c r="P5" t="n">
-        <v>336.3729387614053</v>
+        <v>336.3759654932337</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21503,28 +21556,28 @@
         <v>0.1923</v>
       </c>
       <c r="I6" t="n">
-        <v>1.185111348960656</v>
+        <v>1.186365866273013</v>
       </c>
       <c r="J6" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K6" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6278199111911578</v>
+        <v>0.629096926952136</v>
       </c>
       <c r="M6" t="n">
-        <v>5.428689940301484</v>
+        <v>5.423627912442407</v>
       </c>
       <c r="N6" t="n">
-        <v>52.99458158404502</v>
+        <v>52.90440803537884</v>
       </c>
       <c r="O6" t="n">
-        <v>7.279737741433068</v>
+        <v>7.273541643200982</v>
       </c>
       <c r="P6" t="n">
-        <v>337.8760416287541</v>
+        <v>337.8633603393012</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21581,28 +21634,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.148350339927102</v>
+        <v>1.149843946932414</v>
       </c>
       <c r="J7" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K7" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4640422939713702</v>
+        <v>0.4655467817456744</v>
       </c>
       <c r="M7" t="n">
-        <v>7.183108216791905</v>
+        <v>7.175841812628295</v>
       </c>
       <c r="N7" t="n">
-        <v>97.56518866264929</v>
+        <v>97.38757593074946</v>
       </c>
       <c r="O7" t="n">
-        <v>9.877509233741534</v>
+        <v>9.868514373032522</v>
       </c>
       <c r="P7" t="n">
-        <v>338.2377092984458</v>
+        <v>338.2226631637752</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21659,28 +21712,28 @@
         <v>0.1378</v>
       </c>
       <c r="I8" t="n">
-        <v>3.779444990957221</v>
+        <v>3.822842420912077</v>
       </c>
       <c r="J8" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K8" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1170611013694215</v>
+        <v>0.1196221126533539</v>
       </c>
       <c r="M8" t="n">
-        <v>73.87963154602365</v>
+        <v>73.92407656993953</v>
       </c>
       <c r="N8" t="n">
-        <v>7004.902422920471</v>
+        <v>7003.989612901436</v>
       </c>
       <c r="O8" t="n">
-        <v>83.69529510623921</v>
+        <v>83.68984175454889</v>
       </c>
       <c r="P8" t="n">
-        <v>230.3466021795195</v>
+        <v>229.9139735361402</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21718,7 +21771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I460"/>
+  <dimension ref="A1:I461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43153,7 +43206,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>-41.06299225851277,172.1039848772747</t>
+          <t>-41.063026644165106,172.10369421606956</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -43200,10 +43253,57 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>-41.06296134974526,172.10424614288394</t>
+          <t>-41.063026644165106,172.10369421606956</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:06+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>-41.06705944105601,172.10437575980842</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>-41.06637752769713,172.10434499146936</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>-41.06569161534045,172.104347968022</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-41.065017951229294,172.10424734923757</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>-41.06435346110891,172.10406912428323</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>-41.06368509713818,172.1039235879524</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>-41.06302760394824,172.10368610294924</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0337/nzd0337.xlsx
+++ b/data/nzd0337/nzd0337.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I461"/>
+  <dimension ref="A1:I466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15587,6 +15587,171 @@
         <v>380.9</v>
       </c>
       <c r="I461" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>393.38</v>
+      </c>
+      <c r="C462" t="n">
+        <v>383.98</v>
+      </c>
+      <c r="D462" t="n">
+        <v>372.05</v>
+      </c>
+      <c r="E462" t="n">
+        <v>368.12</v>
+      </c>
+      <c r="F462" t="n">
+        <v>370.09</v>
+      </c>
+      <c r="G462" t="n">
+        <v>370.24</v>
+      </c>
+      <c r="H462" t="n">
+        <v>357.26</v>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>393.56</v>
+      </c>
+      <c r="C463" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="D463" t="n">
+        <v>373.1</v>
+      </c>
+      <c r="E463" t="n">
+        <v>369.74</v>
+      </c>
+      <c r="F463" t="n">
+        <v>370.8</v>
+      </c>
+      <c r="G463" t="n">
+        <v>371.39</v>
+      </c>
+      <c r="H463" t="n">
+        <v>331.23</v>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>393.7</v>
+      </c>
+      <c r="C464" t="n">
+        <v>385.19</v>
+      </c>
+      <c r="D464" t="n">
+        <v>372.49</v>
+      </c>
+      <c r="E464" t="n">
+        <v>369.34</v>
+      </c>
+      <c r="F464" t="n">
+        <v>371.26</v>
+      </c>
+      <c r="G464" t="n">
+        <v>372.74</v>
+      </c>
+      <c r="H464" t="n">
+        <v>304.99</v>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>393.7</v>
+      </c>
+      <c r="C465" t="n">
+        <v>385.19</v>
+      </c>
+      <c r="D465" t="n">
+        <v>372.49</v>
+      </c>
+      <c r="E465" t="n">
+        <v>369.34</v>
+      </c>
+      <c r="F465" t="n">
+        <v>371.26</v>
+      </c>
+      <c r="G465" t="n">
+        <v>372.74</v>
+      </c>
+      <c r="H465" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>393.7</v>
+      </c>
+      <c r="C466" t="n">
+        <v>385.19</v>
+      </c>
+      <c r="D466" t="n">
+        <v>372.49</v>
+      </c>
+      <c r="E466" t="n">
+        <v>369.34</v>
+      </c>
+      <c r="F466" t="n">
+        <v>371.26</v>
+      </c>
+      <c r="G466" t="n">
+        <v>372.74</v>
+      </c>
+      <c r="H466" t="n">
+        <v>271.84</v>
+      </c>
+      <c r="I466" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15603,7 +15768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B547"/>
+  <dimension ref="A1:B551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21076,6 +21241,46 @@
       </c>
       <c r="B547" t="n">
         <v>1.75</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -21244,28 +21449,28 @@
         <v>0.0805</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7485468616047306</v>
+        <v>0.7445168351580558</v>
       </c>
       <c r="J2" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K2" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="L2" t="n">
-        <v>0.359468995335179</v>
+        <v>0.3611645486439942</v>
       </c>
       <c r="M2" t="n">
-        <v>6.173349842211572</v>
+        <v>6.129158161430833</v>
       </c>
       <c r="N2" t="n">
-        <v>64.75690879181066</v>
+        <v>64.11605069891156</v>
       </c>
       <c r="O2" t="n">
-        <v>8.047167749699932</v>
+        <v>8.007249883631181</v>
       </c>
       <c r="P2" t="n">
-        <v>375.8551068506455</v>
+        <v>375.8954249758864</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21322,28 +21527,28 @@
         <v>0.1602</v>
       </c>
       <c r="I3" t="n">
-        <v>1.220822361386465</v>
+        <v>1.225738483765159</v>
       </c>
       <c r="J3" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K3" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6016350851996568</v>
+        <v>0.6077986884217776</v>
       </c>
       <c r="M3" t="n">
-        <v>6.178299924802202</v>
+        <v>6.140349976068299</v>
       </c>
       <c r="N3" t="n">
-        <v>63.23724918089884</v>
+        <v>62.63601476035399</v>
       </c>
       <c r="O3" t="n">
-        <v>7.952185182759443</v>
+        <v>7.914291804094287</v>
       </c>
       <c r="P3" t="n">
-        <v>349.3428103522193</v>
+        <v>349.2930735790218</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21400,28 +21605,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.319963283889876</v>
+        <v>1.318010209515406</v>
       </c>
       <c r="J4" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K4" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6607782929658028</v>
+        <v>0.6643202902594357</v>
       </c>
       <c r="M4" t="n">
-        <v>5.727760049235087</v>
+        <v>5.674435385604812</v>
       </c>
       <c r="N4" t="n">
-        <v>56.83025445729258</v>
+        <v>56.22375000233025</v>
       </c>
       <c r="O4" t="n">
-        <v>7.538584380193179</v>
+        <v>7.498249795941066</v>
       </c>
       <c r="P4" t="n">
-        <v>338.254783861405</v>
+        <v>338.2747215087592</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21478,28 +21683,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1.295635524688633</v>
+        <v>1.292235852032789</v>
       </c>
       <c r="J5" t="n">
+        <v>465</v>
+      </c>
+      <c r="K5" t="n">
         <v>460</v>
       </c>
-      <c r="K5" t="n">
-        <v>455</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6156832696930499</v>
+        <v>0.6187966776075877</v>
       </c>
       <c r="M5" t="n">
-        <v>5.671664461011424</v>
+        <v>5.628684475770465</v>
       </c>
       <c r="N5" t="n">
-        <v>66.86973438749045</v>
+        <v>66.1845840193064</v>
       </c>
       <c r="O5" t="n">
-        <v>8.177391661617442</v>
+        <v>8.135390833838679</v>
       </c>
       <c r="P5" t="n">
-        <v>336.3759654932337</v>
+        <v>336.4104987485872</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21556,28 +21761,28 @@
         <v>0.1923</v>
       </c>
       <c r="I6" t="n">
-        <v>1.186365866273013</v>
+        <v>1.188648265402663</v>
       </c>
       <c r="J6" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K6" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L6" t="n">
-        <v>0.629096926952136</v>
+        <v>0.6343460123775146</v>
       </c>
       <c r="M6" t="n">
-        <v>5.423627912442407</v>
+        <v>5.377002531849868</v>
       </c>
       <c r="N6" t="n">
-        <v>52.90440803537884</v>
+        <v>52.3498973433983</v>
       </c>
       <c r="O6" t="n">
-        <v>7.273541643200982</v>
+        <v>7.23532289144018</v>
       </c>
       <c r="P6" t="n">
-        <v>337.8633603393012</v>
+        <v>337.8401575407615</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21634,28 +21839,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.149843946932414</v>
+        <v>1.155050167644589</v>
       </c>
       <c r="J7" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K7" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4655467817456744</v>
+        <v>0.4722703451810182</v>
       </c>
       <c r="M7" t="n">
-        <v>7.175841812628295</v>
+        <v>7.127213658100066</v>
       </c>
       <c r="N7" t="n">
-        <v>97.38757593074946</v>
+        <v>96.42817761368356</v>
       </c>
       <c r="O7" t="n">
-        <v>9.868514373032522</v>
+        <v>9.819785008526591</v>
       </c>
       <c r="P7" t="n">
-        <v>338.2226631637752</v>
+        <v>338.1699142713449</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21712,28 +21917,28 @@
         <v>0.1378</v>
       </c>
       <c r="I8" t="n">
-        <v>3.822842420912077</v>
+        <v>3.784029772385005</v>
       </c>
       <c r="J8" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K8" t="n">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1196221126533539</v>
+        <v>0.1192214630060865</v>
       </c>
       <c r="M8" t="n">
-        <v>73.92407656993953</v>
+        <v>73.51495461840891</v>
       </c>
       <c r="N8" t="n">
-        <v>7003.989612901436</v>
+        <v>6942.942392834786</v>
       </c>
       <c r="O8" t="n">
-        <v>83.68984175454889</v>
+        <v>83.32432053629232</v>
       </c>
       <c r="P8" t="n">
-        <v>229.9139735361402</v>
+        <v>230.3043833383163</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21771,7 +21976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I461"/>
+  <dimension ref="A1:I466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43309,6 +43514,241 @@
         </is>
       </c>
     </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>-41.0670555044544,172.1044090373744</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>-41.06637402230635,172.10437462348202</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>-41.06568901410665,172.1043699566262</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>-41.06501512743834,172.10427121897737</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>-41.06434944106576,172.10410310599025</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>-41.063681216221596,172.10395639349412</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>-41.062994720616736,172.10396406537765</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>-41.06705575483923,172.10440692078024</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>-41.06637488474447,172.10436733306648</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>-41.06569047469299,172.10435761008392</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-41.065017380907385,172.10425217021967</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>-41.06435042868976,172.10409475754355</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>-41.06368281588369,172.10394287149705</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>-41.06295851200681,172.10427012945377</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>-41.067055949582986,172.10440527454028</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>-41.06637570545129,172.10436039541284</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>-41.06568962616205,172.1043647828371</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-41.06501682449556,172.10425687361675</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>-41.064351068558494,172.10408934869065</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>-41.06368469374586,172.1039269978476</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>-41.06292201045321,172.10457866241134</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>-41.067055949582986,172.10440527454028</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>-41.06637570545129,172.10436039541284</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>-41.06568962616205,172.1043647828371</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-41.06501682449556,172.10425687361675</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>-41.064351068558494,172.10408934869065</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>-41.06368469374586,172.1039269978476</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>-41.062895941381406,172.10479900930068</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>-41.067055949582986,172.10440527454028</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>-41.06637570545129,172.10436039541284</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>-41.06568962616205,172.1043647828371</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>-41.06501682449556,172.10425687361675</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>-41.064351068558494,172.10408934869065</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>-41.06368469374586,172.1039269978476</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>-41.062875895451896,172.10496844348162</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
